--- a/data/gravel/Ritchey 29er 2025.xlsx
+++ b/data/gravel/Ritchey 29er 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19CAFE6-9E68-5841-8326-0AB22E1FCF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B818C7E-ABD0-D342-81E7-E545016A3F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32660" yWindow="-21440" windowWidth="24960" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>corrected</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1123,9 @@
       <c r="F22" s="7">
         <v>483</v>
       </c>
-      <c r="G22" s="7"/>
+      <c r="G22" s="7" t="s">
+        <v>103</v>
+      </c>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8">
@@ -1348,6 +1353,9 @@
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="B46" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:8">

--- a/data/gravel/Ritchey 29er 2025.xlsx
+++ b/data/gravel/Ritchey 29er 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B818C7E-ABD0-D342-81E7-E545016A3F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDF859D-397C-F54A-9610-FAD0FB4584CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32660" yWindow="-21440" windowWidth="24960" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>corrected</t>
+  </si>
+  <si>
+    <t>https://cdn.sanity.io/images/pbcwwn3b/production/1a343351b24b8d26c63c5ff6bc07d341efd56423-1180x640.png?w=1920&amp;q=75&amp;auto=format</t>
   </si>
 </sst>
 </file>
@@ -773,6 +776,11 @@
         <v>98</v>
       </c>
     </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Ritchey 29er 2025.xlsx
+++ b/data/gravel/Ritchey 29er 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDF859D-397C-F54A-9610-FAD0FB4584CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F22C11-78BF-5C49-9197-5E9ACDA43F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32660" yWindow="-21440" windowWidth="24960" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://cdn.sanity.io/images/pbcwwn3b/production/1a343351b24b8d26c63c5ff6bc07d341efd56423-1180x640.png?w=1920&amp;q=75&amp;auto=format</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>San Carlos, California, USA</t>
   </si>
 </sst>
 </file>
@@ -728,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1539,6 +1545,14 @@
         <v>74</v>
       </c>
     </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Ritchey 29er 2025.xlsx
+++ b/data/gravel/Ritchey 29er 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F22C11-78BF-5C49-9197-5E9ACDA43F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFCEC1A-AF97-7748-8469-E0A1829B7064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>San Carlos, California, USA</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1467,6 +1470,9 @@
       <c r="A61" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B61" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">

--- a/data/gravel/Ritchey 29er 2025.xlsx
+++ b/data/gravel/Ritchey 29er 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFCEC1A-AF97-7748-8469-E0A1829B7064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85AEE78-5BB3-454A-A056-355D8E813BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -737,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1403,159 +1421,189 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="1">
-        <v>27.2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="1">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="1">
-        <v>180</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
+      </c>
+      <c r="B61" s="1">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B64" s="1">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1099</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1099</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>106</v>
       </c>
     </row>

--- a/data/gravel/Ritchey 29er 2025.xlsx
+++ b/data/gravel/Ritchey 29er 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85AEE78-5BB3-454A-A056-355D8E813BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4601F34E-620C-5F4F-BE1C-4381C980E667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7600" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -233,9 +233,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>front_center</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -314,9 +311,6 @@
     <t>steel</t>
   </si>
   <si>
-    <t>post_diameter</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -375,6 +369,12 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -800,12 +800,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -813,7 +813,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -821,19 +821,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="E8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -841,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="8">
         <v>575</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="8">
         <v>564</v>
@@ -891,7 +891,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="8">
         <v>380</v>
@@ -919,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="8">
         <v>74</v>
@@ -944,7 +944,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="8">
         <v>100</v>
@@ -969,7 +969,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="8">
         <v>69</v>
@@ -994,7 +994,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="8">
         <v>60</v>
@@ -1019,7 +1019,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="8">
         <v>440</v>
@@ -1041,7 +1041,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="8">
         <v>1098</v>
@@ -1063,7 +1063,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="8">
         <v>760</v>
@@ -1085,7 +1085,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="8">
         <v>589</v>
@@ -1107,7 +1107,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1">
         <v>406</v>
@@ -1127,7 +1127,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" s="1">
         <v>50</v>
@@ -1159,18 +1159,30 @@
         <v>483</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
+      </c>
+      <c r="C23" s="1">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>100</v>
+      </c>
+      <c r="E23" s="1">
+        <v>100</v>
+      </c>
+      <c r="F23" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1198,7 +1210,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -1316,30 +1328,30 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -1349,7 +1361,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -1421,32 +1433,32 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1472,7 +1484,7 @@
         <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1511,7 +1523,7 @@
         <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1519,7 +1531,7 @@
         <v>52</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1578,7 +1590,7 @@
         <v>1099</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1596,15 +1608,15 @@
         <v>65</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
